--- a/measurements/25/Filled_2D_sections/coronal/week25_coronal_Batch_Allmarks.xlsx
+++ b/measurements/25/Filled_2D_sections/coronal/week25_coronal_Batch_Allmarks.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:AA27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,12 +487,72 @@
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v2_mm</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_min_mm</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_max_mm</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_mean_mm</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Mean</t>
         </is>
@@ -506,17 +566,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4.610053539559786</v>
+        <v>1757.256235827664</v>
       </c>
       <c r="D2" t="n">
-        <v>11.19517286521632</v>
+        <v>218.5724226066044</v>
       </c>
       <c r="E2" t="n">
-        <v>9.453783407443908</v>
+        <v>184.5738665262858</v>
       </c>
       <c r="F2" t="n">
         <v>1.184200270169216</v>
@@ -525,24 +585,48 @@
         <v>0.4622258452831871</v>
       </c>
       <c r="H2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I2" t="n">
+        <v>5.598958333333333</v>
+      </c>
+      <c r="J2" t="n">
+        <v>11.6313244047619</v>
+      </c>
+      <c r="K2" t="n">
+        <v>7.384672619047618</v>
+      </c>
+      <c r="L2" t="n">
         <v>1</v>
       </c>
-      <c r="I2" t="n">
-        <v>0.595750762195122</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.595750762195122</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.595750762195122</v>
-      </c>
-      <c r="N2" t="inlineStr">
+      <c r="M2" t="n">
+        <v>11.6313244047619</v>
+      </c>
+      <c r="O2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P2" t="n">
+        <v>6.469494047619047</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>5.83891369047619</v>
+      </c>
+      <c r="R2" t="n">
+        <v>5.598958333333333</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="inlineStr">
         <is>
           <t>area</t>
         </is>
       </c>
-      <c r="O2" s="2" t="n">
-        <v>4.62410767400357</v>
+      <c r="AA2" s="2" t="n">
+        <v>1762.613378684807</v>
       </c>
     </row>
     <row r="3">
@@ -553,43 +637,67 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4.630577037477692</v>
+        <v>1765.079365079365</v>
       </c>
       <c r="D3" t="n">
-        <v>11.31539072060004</v>
+        <v>220.9195331164769</v>
       </c>
       <c r="E3" t="n">
-        <v>9.447865340767837</v>
+        <v>184.458323319753</v>
       </c>
       <c r="F3" t="n">
         <v>1.197666384148572</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4544706781510751</v>
+        <v>0.4544706781510752</v>
       </c>
       <c r="H3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I3" t="n">
+        <v>5.78125</v>
+      </c>
+      <c r="J3" t="n">
+        <v>11.72805059523809</v>
+      </c>
+      <c r="K3" t="n">
+        <v>7.530226934523808</v>
+      </c>
+      <c r="L3" t="n">
         <v>1</v>
       </c>
-      <c r="I3" t="n">
-        <v>0.6007050304878049</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.6007050304878049</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.6007050304878049</v>
-      </c>
-      <c r="N3" t="inlineStr">
+      <c r="M3" t="n">
+        <v>11.72805059523809</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3</v>
+      </c>
+      <c r="P3" t="n">
+        <v>6.501116071428571</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>6.110491071428571</v>
+      </c>
+      <c r="R3" t="n">
+        <v>5.78125</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="inlineStr">
         <is>
           <t>perimeter</t>
         </is>
       </c>
-      <c r="O3" s="2" t="n">
-        <v>10.9164046145067</v>
+      <c r="AA3" s="2" t="n">
+        <v>213.1298043784641</v>
       </c>
     </row>
     <row r="4">
@@ -600,43 +708,67 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4.643961927424153</v>
+        <v>1770.181405895692</v>
       </c>
       <c r="D4" t="n">
-        <v>11.37008925763572</v>
+        <v>221.9874569347926</v>
       </c>
       <c r="E4" t="n">
-        <v>9.468070858862342</v>
+        <v>184.85281200636</v>
       </c>
       <c r="F4" t="n">
         <v>1.200887638794237</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4514095748038724</v>
+        <v>0.4514095748038723</v>
       </c>
       <c r="H4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I4" t="n">
+        <v>6.296502976190476</v>
+      </c>
+      <c r="J4" t="n">
+        <v>11.28162202380952</v>
+      </c>
+      <c r="K4" t="n">
+        <v>7.670200892857142</v>
+      </c>
+      <c r="L4" t="n">
         <v>1</v>
       </c>
-      <c r="I4" t="n">
-        <v>0.5778391768292683</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.5778391768292683</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.5778391768292683</v>
-      </c>
-      <c r="N4" t="inlineStr">
+      <c r="M4" t="n">
+        <v>11.28162202380952</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3</v>
+      </c>
+      <c r="P4" t="n">
+        <v>6.666666666666666</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>6.436011904761904</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6.296502976190476</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="inlineStr">
         <is>
           <t>perimeter_convex</t>
         </is>
       </c>
-      <c r="O4" s="2" t="n">
-        <v>9.576356156134024</v>
+      <c r="AA4" s="2" t="n">
+        <v>186.9669535245214</v>
       </c>
     </row>
     <row r="5">
@@ -647,17 +779,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4.673706127305175</v>
+        <v>1781.519274376417</v>
       </c>
       <c r="D5" t="n">
-        <v>11.4474447238736</v>
+        <v>223.4977303232465</v>
       </c>
       <c r="E5" t="n">
-        <v>9.502563903971417</v>
+        <v>185.5262476489657</v>
       </c>
       <c r="F5" t="n">
         <v>1.204669059798626</v>
@@ -666,23 +798,47 @@
         <v>0.4481817366964971</v>
       </c>
       <c r="H5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I5" t="n">
+        <v>6.331845238095238</v>
+      </c>
+      <c r="J5" t="n">
+        <v>11.64248511904762</v>
+      </c>
+      <c r="K5" t="n">
+        <v>7.863653273809523</v>
+      </c>
+      <c r="L5" t="n">
         <v>1</v>
       </c>
-      <c r="I5" t="n">
-        <v>0.5963224085365854</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.5963224085365854</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.5963224085365854</v>
-      </c>
-      <c r="N5" t="inlineStr">
+      <c r="M5" t="n">
+        <v>11.64248511904762</v>
+      </c>
+      <c r="O5" t="n">
+        <v>3</v>
+      </c>
+      <c r="P5" t="n">
+        <v>6.813616071428571</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>6.666666666666666</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6.331845238095238</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>LGI</t>
         </is>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="AA5" s="2" t="n">
         <v>1.140138394891516</v>
       </c>
     </row>
@@ -694,17 +850,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4.73111243307555</v>
+        <v>1803.401360544218</v>
       </c>
       <c r="D6" t="n">
-        <v>11.51051267763463</v>
+        <v>224.7290570395333</v>
       </c>
       <c r="E6" t="n">
-        <v>9.510933294528868</v>
+        <v>185.6896500360398</v>
       </c>
       <c r="F6" t="n">
         <v>1.21024008067179</v>
@@ -713,23 +869,47 @@
         <v>0.4487286491401198</v>
       </c>
       <c r="H6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I6" t="n">
+        <v>6.19047619047619</v>
+      </c>
+      <c r="J6" t="n">
+        <v>10.92633928571428</v>
+      </c>
+      <c r="K6" t="n">
+        <v>8.060360863095237</v>
+      </c>
+      <c r="L6" t="n">
         <v>1</v>
       </c>
-      <c r="I6" t="n">
-        <v>0.559641768292683</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.559641768292683</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.559641768292683</v>
-      </c>
-      <c r="N6" t="inlineStr">
+      <c r="M6" t="n">
+        <v>10.92633928571428</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3</v>
+      </c>
+      <c r="P6" t="n">
+        <v>7.717633928571428</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>7.406994047619047</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6.19047619047619</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="inlineStr">
         <is>
           <t>Compactness</t>
         </is>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="AA6" s="2" t="n">
         <v>0.4882570016866641</v>
       </c>
     </row>
@@ -741,43 +921,67 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4.762641284949435</v>
+        <v>1815.419501133787</v>
       </c>
       <c r="D7" t="n">
-        <v>11.24640469434785</v>
+        <v>219.5726630801246</v>
       </c>
       <c r="E7" t="n">
-        <v>9.571549906963256</v>
+        <v>186.8731172311874</v>
       </c>
       <c r="F7" t="n">
         <v>1.174982610304956</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4731842948919335</v>
+        <v>0.4731842948919336</v>
       </c>
       <c r="H7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I7" t="n">
+        <v>6.008184523809524</v>
+      </c>
+      <c r="J7" t="n">
+        <v>11.17559523809524</v>
+      </c>
+      <c r="K7" t="n">
+        <v>8.215680803571429</v>
+      </c>
+      <c r="L7" t="n">
         <v>1</v>
       </c>
-      <c r="I7" t="n">
-        <v>0.5724085365853658</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.5724085365853658</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.5724085365853658</v>
-      </c>
-      <c r="N7" t="inlineStr">
+      <c r="M7" t="n">
+        <v>11.17559523809524</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3</v>
+      </c>
+      <c r="P7" t="n">
+        <v>7.875744047619047</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>7.803199404761904</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6.008184523809524</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>Sulci_count</t>
         </is>
       </c>
-      <c r="O7" s="2" t="n">
-        <v>0.7</v>
+      <c r="AA7" s="2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -788,17 +992,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4.782272456870911</v>
+        <v>1822.902494331066</v>
       </c>
       <c r="D8" t="n">
-        <v>11.04781602068645</v>
+        <v>215.6954556419736</v>
       </c>
       <c r="E8" t="n">
-        <v>9.606042905551632</v>
+        <v>187.5465519655318</v>
       </c>
       <c r="F8" t="n">
         <v>1.150090222301795</v>
@@ -807,15 +1011,48 @@
         <v>0.4923696927649781</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="I8" t="n">
+        <v>6.19047619047619</v>
+      </c>
+      <c r="J8" t="n">
+        <v>9.317336309523808</v>
+      </c>
+      <c r="K8" t="n">
+        <v>7.816220238095237</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>9.317336309523808</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3</v>
+      </c>
+      <c r="P8" t="n">
+        <v>7.935267857142857</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>7.821800595238095</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6.19047619047619</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="inlineStr">
         <is>
           <t>min_depth_mm</t>
         </is>
       </c>
-      <c r="O8" s="2" t="n">
-        <v>0.5601045296167247</v>
+      <c r="AA8" s="2" t="n">
+        <v>5.301618303571429</v>
       </c>
     </row>
     <row r="9">
@@ -826,17 +1063,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4.788518738845926</v>
+        <v>1825.283446712018</v>
       </c>
       <c r="D9" t="n">
-        <v>10.91576204067323</v>
+        <v>213.1172588893345</v>
       </c>
       <c r="E9" t="n">
-        <v>9.606042902644088</v>
+        <v>187.5465519087655</v>
       </c>
       <c r="F9" t="n">
         <v>1.136343253023432</v>
@@ -845,15 +1082,45 @@
         <v>0.5050134397424042</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="I9" t="n">
+        <v>6.19047619047619</v>
+      </c>
+      <c r="J9" t="n">
+        <v>8.037574404761905</v>
+      </c>
+      <c r="K9" t="n">
+        <v>7.496744791666666</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>4</v>
+      </c>
+      <c r="S9" t="n">
+        <v>6.19047619047619</v>
+      </c>
+      <c r="T9" t="n">
+        <v>8.037574404761905</v>
+      </c>
+      <c r="U9" t="n">
+        <v>7.496744791666666</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="inlineStr">
         <is>
           <t>max_depth_mm</t>
         </is>
       </c>
-      <c r="O9" s="2" t="n">
-        <v>0.5601045296167247</v>
+      <c r="AA9" s="2" t="n">
+        <v>10.30394345238095</v>
       </c>
     </row>
     <row r="10">
@@ -864,34 +1131,67 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4.796252230814991</v>
+        <v>1828.231292517007</v>
       </c>
       <c r="D10" t="n">
-        <v>10.75758445553663</v>
+        <v>210.0290298461914</v>
       </c>
       <c r="E10" t="n">
-        <v>9.565631849009817</v>
+        <v>186.7575741949535</v>
       </c>
       <c r="F10" t="n">
         <v>1.124607827830025</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5208136397481101</v>
+        <v>0.5208136397481102</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="I10" t="n">
+        <v>5.238095238095238</v>
+      </c>
+      <c r="J10" t="n">
+        <v>8.037574404761905</v>
+      </c>
+      <c r="K10" t="n">
+        <v>7.200055803571428</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>8.037574404761905</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3</v>
+      </c>
+      <c r="P10" t="n">
+        <v>7.797619047619047</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>7.726934523809524</v>
+      </c>
+      <c r="R10" t="n">
+        <v>5.238095238095238</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="inlineStr">
         <is>
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="O10" s="2" t="n">
-        <v>0.5601045296167247</v>
+      <c r="AA10" s="2" t="n">
+        <v>7.43701171875</v>
       </c>
     </row>
     <row r="11">
@@ -902,26 +1202,67 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4.784651992861392</v>
+        <v>1823.809523809524</v>
       </c>
       <c r="D11" t="n">
-        <v>10.83248856009507</v>
+        <v>211.4914433161418</v>
       </c>
       <c r="E11" t="n">
-        <v>9.620330409305852</v>
+        <v>187.8254984673999</v>
       </c>
       <c r="F11" t="n">
         <v>1.125999638184639</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5123936525851576</v>
+        <v>0.5123936525851577</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="I11" t="n">
+        <v>5.238095238095238</v>
+      </c>
+      <c r="J11" t="n">
+        <v>8.696056547619047</v>
+      </c>
+      <c r="K11" t="n">
+        <v>7.490699404761905</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>8.696056547619047</v>
+      </c>
+      <c r="N11" t="n">
+        <v>8.327752976190476</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2</v>
+      </c>
+      <c r="P11" t="n">
+        <v>7.700892857142857</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>5.238095238095238</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="n">
+        <v>1.15</v>
       </c>
     </row>
     <row r="12">
@@ -932,17 +1273,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4.766805472932778</v>
+        <v>1817.006802721088</v>
       </c>
       <c r="D12" t="n">
-        <v>10.80391358747715</v>
+        <v>210.9335509936015</v>
       </c>
       <c r="E12" t="n">
-        <v>9.675028940526451</v>
+        <v>188.8934221721831</v>
       </c>
       <c r="F12" t="n">
         <v>1.1166802346422</v>
@@ -951,7 +1292,48 @@
         <v>0.5131863419678299</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="I12" t="n">
+        <v>5.238095238095238</v>
+      </c>
+      <c r="J12" t="n">
+        <v>9.19828869047619</v>
+      </c>
+      <c r="K12" t="n">
+        <v>7.580915178571428</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" t="n">
+        <v>9.19828869047619</v>
+      </c>
+      <c r="N12" t="n">
+        <v>8.301711309523808</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2</v>
+      </c>
+      <c r="P12" t="n">
+        <v>7.585565476190475</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>5.238095238095238</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="n">
+        <v>10.42322603383458</v>
       </c>
     </row>
     <row r="13">
@@ -962,26 +1344,67 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4.736763831052945</v>
+        <v>1805.555555555555</v>
       </c>
       <c r="D13" t="n">
-        <v>10.72900948582626</v>
+        <v>209.4711375804174</v>
       </c>
       <c r="E13" t="n">
-        <v>9.75238438931907</v>
+        <v>190.403695220039</v>
       </c>
       <c r="F13" t="n">
-        <v>1.100142186517669</v>
+        <v>1.100142186517668</v>
       </c>
       <c r="G13" t="n">
         <v>0.5170973800954207</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="I13" t="n">
+        <v>5.238095238095238</v>
+      </c>
+      <c r="J13" t="n">
+        <v>9.696800595238095</v>
+      </c>
+      <c r="K13" t="n">
+        <v>7.658110119047619</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2</v>
+      </c>
+      <c r="M13" t="n">
+        <v>9.696800595238095</v>
+      </c>
+      <c r="N13" t="n">
+        <v>8.227306547619047</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2</v>
+      </c>
+      <c r="P13" t="n">
+        <v>7.470238095238095</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>5.238095238095238</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>Primary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="n">
+        <v>8.228701636904761</v>
       </c>
     </row>
     <row r="14">
@@ -992,35 +1415,67 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4.678167757287329</v>
+        <v>1783.219954648526</v>
       </c>
       <c r="D14" t="n">
-        <v>10.80391361364504</v>
+        <v>210.9335515044984</v>
       </c>
       <c r="E14" t="n">
-        <v>9.744014995854076</v>
+        <v>190.2402927761986</v>
       </c>
       <c r="F14" t="n">
         <v>1.108774321287676</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5036437506159351</v>
+        <v>0.5036437506159352</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5252477134146342</v>
+        <v>4.761904761904762</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5252477134146342</v>
+        <v>10.25483630952381</v>
       </c>
       <c r="K14" t="n">
-        <v>0.5252477134146342</v>
+        <v>7.601376488095238</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2</v>
+      </c>
+      <c r="M14" t="n">
+        <v>10.25483630952381</v>
+      </c>
+      <c r="N14" t="n">
+        <v>8.058035714285714</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2</v>
+      </c>
+      <c r="P14" t="n">
+        <v>7.330729166666666</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>4.761904761904762</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="n">
+        <v>2.85</v>
       </c>
     </row>
     <row r="15">
@@ -1031,17 +1486,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4.64069006543724</v>
+        <v>1768.934240362812</v>
       </c>
       <c r="D15" t="n">
-        <v>10.76350250476744</v>
+        <v>210.1445727121262</v>
       </c>
       <c r="E15" t="n">
-        <v>9.723809434146416</v>
+        <v>189.8458032380967</v>
       </c>
       <c r="F15" t="n">
         <v>1.106922402959689</v>
@@ -1050,16 +1505,48 @@
         <v>0.503367528075786</v>
       </c>
       <c r="H15" t="n">
+        <v>4</v>
+      </c>
+      <c r="I15" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="J15" t="n">
+        <v>10.71986607142857</v>
+      </c>
+      <c r="K15" t="n">
+        <v>7.408854166666666</v>
+      </c>
+      <c r="L15" t="n">
         <v>1</v>
       </c>
-      <c r="I15" t="n">
-        <v>0.5490663109756098</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.5490663109756098</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.5490663109756098</v>
+      <c r="M15" t="n">
+        <v>10.71986607142857</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3</v>
+      </c>
+      <c r="P15" t="n">
+        <v>7.507440476190475</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>7.122395833333333</v>
+      </c>
+      <c r="R15" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="n">
+        <v>7.124451754385964</v>
       </c>
     </row>
     <row r="16">
@@ -1070,17 +1557,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4.607079119571684</v>
+        <v>1756.122448979592</v>
       </c>
       <c r="D16" t="n">
-        <v>10.85514541370113</v>
+        <v>211.9337914103553</v>
       </c>
       <c r="E16" t="n">
-        <v>9.729727480469681</v>
+        <v>189.9613460472652</v>
       </c>
       <c r="F16" t="n">
         <v>1.115667980988212</v>
@@ -1089,16 +1576,48 @@
         <v>0.4913197741679368</v>
       </c>
       <c r="H16" t="n">
+        <v>4</v>
+      </c>
+      <c r="I16" t="n">
+        <v>4.761904761904762</v>
+      </c>
+      <c r="J16" t="n">
+        <v>10.68638392857143</v>
+      </c>
+      <c r="K16" t="n">
+        <v>7.389787946428572</v>
+      </c>
+      <c r="L16" t="n">
         <v>1</v>
       </c>
-      <c r="I16" t="n">
-        <v>0.5473513719512195</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.5473513719512195</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.5473513719512195</v>
+      <c r="M16" t="n">
+        <v>10.68638392857143</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3</v>
+      </c>
+      <c r="P16" t="n">
+        <v>7.429315476190475</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>6.681547619047619</v>
+      </c>
+      <c r="R16" t="n">
+        <v>4.761904761904762</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="n">
+        <v>6.27829338972431</v>
       </c>
     </row>
     <row r="17">
@@ -1109,17 +1628,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4.566924449732302</v>
+        <v>1740.816326530612</v>
       </c>
       <c r="D17" t="n">
-        <v>10.7718719360305</v>
+        <v>210.3079758939289</v>
       </c>
       <c r="E17" t="n">
-        <v>9.680947013017608</v>
+        <v>189.0089654922485</v>
       </c>
       <c r="F17" t="n">
         <v>1.112687831215889</v>
@@ -1128,16 +1647,48 @@
         <v>0.4945968294859286</v>
       </c>
       <c r="H17" t="n">
+        <v>4</v>
+      </c>
+      <c r="I17" t="n">
+        <v>4.761904761904762</v>
+      </c>
+      <c r="J17" t="n">
+        <v>10.84449404761905</v>
+      </c>
+      <c r="K17" t="n">
+        <v>7.311662946428572</v>
+      </c>
+      <c r="L17" t="n">
         <v>1</v>
       </c>
-      <c r="I17" t="n">
-        <v>0.5554496951219512</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.5554496951219512</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.5554496951219512</v>
+      <c r="M17" t="n">
+        <v>10.84449404761905</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3</v>
+      </c>
+      <c r="P17" t="n">
+        <v>7.207961309523809</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>6.432291666666666</v>
+      </c>
+      <c r="R17" t="n">
+        <v>4.761904761904762</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="n">
+        <v>5.291046626984127</v>
       </c>
     </row>
     <row r="18">
@@ -1148,17 +1699,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4.46133254015467</v>
+        <v>1700.566893424036</v>
       </c>
       <c r="D18" t="n">
-        <v>10.63981793857202</v>
+        <v>207.7297788006919</v>
       </c>
       <c r="E18" t="n">
-        <v>9.583386014147504</v>
+        <v>187.104203133356</v>
       </c>
       <c r="F18" t="n">
         <v>1.11023576874238</v>
@@ -1167,16 +1718,48 @@
         <v>0.4952289979518165</v>
       </c>
       <c r="H18" t="n">
+        <v>4</v>
+      </c>
+      <c r="I18" t="n">
+        <v>4.761904761904762</v>
+      </c>
+      <c r="J18" t="n">
+        <v>10.81659226190476</v>
+      </c>
+      <c r="K18" t="n">
+        <v>7.051246279761904</v>
+      </c>
+      <c r="L18" t="n">
         <v>1</v>
       </c>
-      <c r="I18" t="n">
-        <v>0.5540205792682927</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.5540205792682927</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0.5540205792682927</v>
+      <c r="M18" t="n">
+        <v>10.81659226190476</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3</v>
+      </c>
+      <c r="P18" t="n">
+        <v>6.681547619047619</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>5.944940476190476</v>
+      </c>
+      <c r="R18" t="n">
+        <v>4.761904761904762</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>Secondary_min_mm</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="n">
+        <v>6.19047619047619</v>
       </c>
     </row>
     <row r="19">
@@ -1187,35 +1770,67 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4.386079714455682</v>
+        <v>1671.8820861678</v>
       </c>
       <c r="D19" t="n">
-        <v>10.65410540452818</v>
+        <v>208.0087245645977</v>
       </c>
       <c r="E19" t="n">
-        <v>9.54297494306797</v>
+        <v>186.3152250789461</v>
       </c>
       <c r="F19" t="n">
         <v>1.116434389494791</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4855706255117337</v>
+        <v>0.4855706255117336</v>
       </c>
       <c r="H19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I19" t="n">
+        <v>4.761904761904762</v>
+      </c>
+      <c r="J19" t="n">
+        <v>10.67522321428571</v>
+      </c>
+      <c r="K19" t="n">
+        <v>6.933593749999999</v>
+      </c>
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="I19" t="n">
-        <v>0.5467797256097561</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.5467797256097561</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0.5467797256097561</v>
+      <c r="M19" t="n">
+        <v>10.67522321428571</v>
+      </c>
+      <c r="O19" t="n">
+        <v>3</v>
+      </c>
+      <c r="P19" t="n">
+        <v>6.582961309523809</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="R19" t="n">
+        <v>4.761904761904762</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>Secondary_max_mm</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="n">
+        <v>8.037574404761905</v>
       </c>
     </row>
     <row r="20">
@@ -1226,17 +1841,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4.311421772754313</v>
+        <v>1643.424036281179</v>
       </c>
       <c r="D20" t="n">
-        <v>10.42449044309011</v>
+        <v>203.5257657936641</v>
       </c>
       <c r="E20" t="n">
-        <v>9.451332037041828</v>
+        <v>184.5260064374833</v>
       </c>
       <c r="F20" t="n">
         <v>1.102965211912381</v>
@@ -1245,16 +1860,48 @@
         <v>0.4985637560839519</v>
       </c>
       <c r="H20" t="n">
+        <v>4</v>
+      </c>
+      <c r="I20" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="J20" t="n">
+        <v>10.35528273809524</v>
+      </c>
+      <c r="K20" t="n">
+        <v>6.682942708333332</v>
+      </c>
+      <c r="L20" t="n">
         <v>1</v>
       </c>
-      <c r="I20" t="n">
-        <v>0.5303925304878049</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.5303925304878049</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0.5303925304878049</v>
+      <c r="M20" t="n">
+        <v>10.35528273809524</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3</v>
+      </c>
+      <c r="P20" t="n">
+        <v>6.376488095238095</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="R20" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>Secondary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="n">
+        <v>7.496744791666666</v>
       </c>
     </row>
     <row r="21">
@@ -1265,35 +1912,67 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4.123140987507436</v>
+        <v>1571.655328798186</v>
       </c>
       <c r="D21" t="n">
-        <v>10.24365594619658</v>
+        <v>199.9951875209808</v>
       </c>
       <c r="E21" t="n">
-        <v>9.290703096040865</v>
+        <v>181.3899175893693</v>
       </c>
       <c r="F21" t="n">
         <v>1.102570584842153</v>
       </c>
       <c r="G21" t="n">
-        <v>0.4937738459696081</v>
+        <v>0.493773845969608</v>
       </c>
       <c r="H21" t="n">
+        <v>4</v>
+      </c>
+      <c r="I21" t="n">
+        <v>4.110863095238095</v>
+      </c>
+      <c r="J21" t="n">
+        <v>10.35714285714286</v>
+      </c>
+      <c r="K21" t="n">
+        <v>6.393229166666666</v>
+      </c>
+      <c r="L21" t="n">
         <v>1</v>
       </c>
-      <c r="I21" t="n">
-        <v>0.5304878048780488</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.5304878048780488</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.5304878048780488</v>
+      <c r="M21" t="n">
+        <v>10.35714285714286</v>
+      </c>
+      <c r="O21" t="n">
+        <v>3</v>
+      </c>
+      <c r="P21" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>5.390625</v>
+      </c>
+      <c r="R21" t="n">
+        <v>4.110863095238095</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1303,7 +1982,15 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.02439024390243903</v>
+        <v>0.4761904761904762</v>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1326,6 +2013,38 @@
       </c>
       <c r="B24" t="n">
         <v>25</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ScalebarMeasuredPixels:</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldLength:</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldUnit:</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/measurements/25/Filled_2D_sections/coronal/week25_coronal_Batch_Allmarks.xlsx
+++ b/measurements/25/Filled_2D_sections/coronal/week25_coronal_Batch_Allmarks.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Analysis" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -137,6 +138,186 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>67</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2050,4 +2231,1265 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Workbook Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Workbook</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>week25_coronal_Batch_Allmarks.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Axis</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>coronal</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Slice rows analyzed</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>When a sulcus class count exceeds 3, approximate raw sulcus values are reconstructed from count + min/max/mean for summary stats and boxplots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Core Metric Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>20</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1762.613378684807</v>
+      </c>
+      <c r="D10" t="n">
+        <v>68.461337801384</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1571.655328798186</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1828.231292517007</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>perimeter</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C11" t="n">
+        <v>213.1298043784641</v>
+      </c>
+      <c r="D11" t="n">
+        <v>6.620016813106565</v>
+      </c>
+      <c r="E11" t="n">
+        <v>199.9951875209808</v>
+      </c>
+      <c r="F11" t="n">
+        <v>224.7290570395333</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LGI</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.140138394891516</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.0394882147512825</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.100142186517668</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.21024008067179</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Compactness</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>20</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.4882570016866642</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.02370116837361665</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.4481817366964971</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.5208136397481102</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Counts Per Slice</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sulci_count</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>band_axis1_s00_idx0110.png</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>4</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>band_axis1_s01_idx0111.png</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>4</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>4</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>band_axis1_s02_idx0112.png</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>4</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>4</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>band_axis1_s03_idx0113.png</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>4</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>4</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>band_axis1_s04_idx0115.png</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>4</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>band_axis1_s05_idx0116.png</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>4</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>4</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>band_axis1_s06_idx0117.png</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>4</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>4</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>3</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>band_axis1_s07_idx0118.png</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>4</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>4</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>4</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>4</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>band_axis1_s08_idx0120.png</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>4</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>3</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>band_axis1_s09_idx0121.png</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>4</v>
+      </c>
+      <c r="C26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>4</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>band_axis1_s10_idx0122.png</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>4</v>
+      </c>
+      <c r="C27" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>4</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>band_axis1_s11_idx0123.png</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>4</v>
+      </c>
+      <c r="C28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>4</v>
+      </c>
+      <c r="H28" t="n">
+        <v>2</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>band_axis1_s12_idx0125.png</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>4</v>
+      </c>
+      <c r="C29" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>4</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>band_axis1_s13_idx0126.png</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>4</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="n">
+        <v>3</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>4</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="n">
+        <v>3</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>band_axis1_s14_idx0127.png</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>4</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="n">
+        <v>3</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>4</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="n">
+        <v>3</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>band_axis1_s15_idx0128.png</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>4</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="n">
+        <v>3</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>4</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>3</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>band_axis1_s16_idx0130.png</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>4</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="n">
+        <v>3</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>4</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" t="n">
+        <v>3</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>band_axis1_s17_idx0131.png</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>4</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>4</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>3</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>band_axis1_s18_idx0132.png</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>4</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="n">
+        <v>3</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>4</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="n">
+        <v>3</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>band_axis1_s19_idx0134.png</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>4</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="n">
+        <v>3</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>4</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="n">
+        <v>3</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Count Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>20</v>
+      </c>
+      <c r="C40" t="n">
+        <v>4</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>4</v>
+      </c>
+      <c r="F40" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>20</v>
+      </c>
+      <c r="C41" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.4893604849295929</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>20</v>
+      </c>
+      <c r="C42" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.4893604849295929</v>
+      </c>
+      <c r="E42" t="n">
+        <v>2</v>
+      </c>
+      <c r="F42" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>20</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>20</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sulcus Value Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>primary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>23</v>
+      </c>
+      <c r="C48" t="n">
+        <v>10.04156961697723</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1.255504022137374</v>
+      </c>
+      <c r="E48" t="n">
+        <v>8.037574404761905</v>
+      </c>
+      <c r="F48" t="n">
+        <v>11.72805059523809</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>secondary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>57</v>
+      </c>
+      <c r="C49" t="n">
+        <v>6.386049759816206</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1.105900580651435</v>
+      </c>
+      <c r="E49" t="n">
+        <v>4.110863095238095</v>
+      </c>
+      <c r="F49" t="n">
+        <v>8.037574404761905</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>tertiary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>unclassified_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>